--- a/output/pdf_financials_xlsx/QAI.xlsx
+++ b/output/pdf_financials_xlsx/QAI.xlsx
@@ -1768,7 +1768,7 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>1.389379</v>
+        <v>2.450503</v>
       </c>
     </row>
     <row r="93">
@@ -2828,7 +2828,11 @@
           <t>Warrant reserve (Note 7)* 545,783</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -2856,7 +2860,11 @@
           <t>Share-based payment reserve (Note 6) 1,061,124</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QAI.xlsx
+++ b/output/pdf_financials_xlsx/QAI.xlsx
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-1.163753</v>
+        <v>-1.175709</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-1.163753</v>
@@ -3078,7 +3078,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>-1.175709</v>
       </c>
